--- a/Tubex Records/Tubex_Sep26.xlsx
+++ b/Tubex Records/Tubex_Sep26.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Alpha\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Alpha\Tubex Records\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_45550E76BB326ABFB74573A29A6CB8D7F84CC5F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A440CAAA-3A4A-4E18-9B90-CF864E05B28A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tubex_Dashboard" sheetId="1" r:id="rId1"/>
@@ -5031,36 +5031,6 @@
     <xf numFmtId="166" fontId="45" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="45" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="30" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="32" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="21" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="37" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="30" fillId="5" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5070,6 +5040,36 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="22" borderId="37" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="50" fillId="21" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="37" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="30" fillId="5" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="30" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="32" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="62" fillId="24" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -5605,22 +5605,22 @@
     </row>
     <row r="2" spans="1:29" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="87"/>
-      <c r="B2" s="329" t="s">
+      <c r="B2" s="325" t="s">
         <v>152</v>
       </c>
-      <c r="C2" s="322"/>
-      <c r="D2" s="322"/>
-      <c r="E2" s="323"/>
-      <c r="F2" s="322"/>
-      <c r="G2" s="324"/>
-      <c r="H2" s="322"/>
-      <c r="I2" s="322"/>
-      <c r="J2" s="322"/>
-      <c r="K2" s="322"/>
-      <c r="L2" s="322"/>
-      <c r="M2" s="322"/>
-      <c r="N2" s="322"/>
-      <c r="O2" s="322"/>
+      <c r="C2" s="326"/>
+      <c r="D2" s="326"/>
+      <c r="E2" s="327"/>
+      <c r="F2" s="326"/>
+      <c r="G2" s="328"/>
+      <c r="H2" s="326"/>
+      <c r="I2" s="326"/>
+      <c r="J2" s="326"/>
+      <c r="K2" s="326"/>
+      <c r="L2" s="326"/>
+      <c r="M2" s="326"/>
+      <c r="N2" s="326"/>
+      <c r="O2" s="326"/>
       <c r="P2" s="87"/>
       <c r="Q2" s="87"/>
       <c r="R2" s="87"/>
@@ -5638,25 +5638,25 @@
     </row>
     <row r="3" spans="1:29" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="87"/>
-      <c r="B3" s="321" t="s">
+      <c r="B3" s="333" t="s">
         <v>153</v>
       </c>
-      <c r="C3" s="322"/>
-      <c r="D3" s="322"/>
-      <c r="E3" s="323"/>
-      <c r="F3" s="322"/>
-      <c r="G3" s="324"/>
-      <c r="H3" s="326">
+      <c r="C3" s="326"/>
+      <c r="D3" s="326"/>
+      <c r="E3" s="327"/>
+      <c r="F3" s="326"/>
+      <c r="G3" s="328"/>
+      <c r="H3" s="335">
         <f ca="1">TODAY()</f>
         <v>46302</v>
       </c>
-      <c r="I3" s="322"/>
-      <c r="J3" s="322"/>
-      <c r="K3" s="322"/>
-      <c r="L3" s="322"/>
-      <c r="M3" s="322"/>
-      <c r="N3" s="322"/>
-      <c r="O3" s="322"/>
+      <c r="I3" s="326"/>
+      <c r="J3" s="326"/>
+      <c r="K3" s="326"/>
+      <c r="L3" s="326"/>
+      <c r="M3" s="326"/>
+      <c r="N3" s="326"/>
+      <c r="O3" s="326"/>
       <c r="P3" s="87"/>
       <c r="Q3" s="87"/>
       <c r="R3" s="87"/>
@@ -5716,21 +5716,21 @@
       </c>
       <c r="E5" s="92"/>
       <c r="F5" s="93"/>
-      <c r="G5" s="328" t="s">
+      <c r="G5" s="331" t="s">
         <v>156</v>
       </c>
-      <c r="H5" s="322"/>
+      <c r="H5" s="326"/>
       <c r="I5" s="94"/>
-      <c r="J5" s="328" t="s">
+      <c r="J5" s="331" t="s">
         <v>157</v>
       </c>
-      <c r="K5" s="322"/>
+      <c r="K5" s="326"/>
       <c r="L5" s="112"/>
-      <c r="M5" s="330" t="s">
+      <c r="M5" s="329" t="s">
         <v>158</v>
       </c>
-      <c r="N5" s="331"/>
-      <c r="O5" s="331"/>
+      <c r="N5" s="330"/>
+      <c r="O5" s="330"/>
       <c r="P5" s="284"/>
       <c r="Q5" s="284"/>
       <c r="R5" s="284"/>
@@ -5748,28 +5748,28 @@
     </row>
     <row r="6" spans="1:29" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="87"/>
-      <c r="B6" s="325">
+      <c r="B6" s="334">
         <f>SUMPRODUCT((Production_Log!$A$3:$A$8961=MAX(Production_Log!$A$3:$A$8961))*(LEFT(Production_Log!$B$3:$B$8961,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8961)))*Production_Log!$H$3:$H$8961)</f>
         <v>15470</v>
       </c>
-      <c r="C6" s="322"/>
+      <c r="C6" s="326"/>
       <c r="D6" s="95">
         <f>SUMIF($B$11:$B$67,"TUBE",$H$11:$H$67)</f>
         <v>419362</v>
       </c>
-      <c r="E6" s="325"/>
-      <c r="F6" s="322"/>
+      <c r="E6" s="334"/>
+      <c r="F6" s="326"/>
       <c r="G6" s="96">
         <f t="array" ref="G6">IFERROR(SUMPRODUCT((Production_Log!$F$3:$F$8961&lt;&gt;0)*(LEFT(Production_Log!$B$3:$B$8961,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8961)))*Production_Log!$I$3:$I$8961)/SUMPRODUCT((Production_Log!$F$3:$F$8961&lt;&gt;0)*(LEFT(Production_Log!$B$3:$B$8961,5)="Print")*(ISERROR(SEARCH("(Varnish)",Production_Log!$D$3:$D$8961)))*(Production_Log!$H$3:$H$8961+Production_Log!$I$3:$I$8961)),"-")</f>
         <v>2.4029118870247411E-2</v>
       </c>
       <c r="H6" s="96"/>
       <c r="I6" s="94"/>
-      <c r="J6" s="325">
+      <c r="J6" s="334">
         <f>SUMIF($B$11:$B$67,"TUBE",$K$11:$K$67)</f>
         <v>491479</v>
       </c>
-      <c r="K6" s="322"/>
+      <c r="K6" s="326"/>
       <c r="L6" s="97"/>
       <c r="M6" s="286" t="s">
         <v>26</v>
@@ -5809,10 +5809,10 @@
       </c>
       <c r="E7" s="98"/>
       <c r="F7" s="99"/>
-      <c r="G7" s="327" t="s">
+      <c r="G7" s="336" t="s">
         <v>163</v>
       </c>
-      <c r="H7" s="322"/>
+      <c r="H7" s="326"/>
       <c r="I7" s="100"/>
       <c r="J7" s="99" t="s">
         <v>157</v>
@@ -5851,13 +5851,13 @@
         <f>SUMPRODUCT((Production_Log!$A$3:$A$8961=MAX(Production_Log!$A$3:$A$8961))*(Production_Log!$B$3:$B$8961="PF Machine")*Production_Log!$H$3:$H$8961)</f>
         <v>11500</v>
       </c>
-      <c r="C8" s="322"/>
+      <c r="C8" s="326"/>
       <c r="D8" s="101">
         <f>SUMIF($B$11:$B$67,"PET",$H$11:$H$67)</f>
         <v>322360</v>
       </c>
       <c r="E8" s="332"/>
-      <c r="F8" s="322"/>
+      <c r="F8" s="326"/>
       <c r="G8" s="102">
         <f t="array" ref="G8">IFERROR(SUMPRODUCT((Production_Log!$B$3:$B$8961="PF Machine")*Production_Log!$I$3:$I$8961)/SUMPRODUCT((Production_Log!$B$3:$B$8961="PF Machine")*(Production_Log!$H$3:$H$8961+Production_Log!$I$3:$I$8961)),0)</f>
         <v>0.21368130139208363</v>
@@ -5868,7 +5868,7 @@
         <f>SUMIF($B$11:$B$67,"PET",$K$11:$K$67)</f>
         <v>285400</v>
       </c>
-      <c r="K8" s="322"/>
+      <c r="K8" s="326"/>
       <c r="L8" s="103"/>
       <c r="M8" s="288" t="s">
         <v>165</v>
@@ -5898,19 +5898,19 @@
     </row>
     <row r="9" spans="1:29" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="87"/>
-      <c r="B9" s="333" t="s">
+      <c r="B9" s="321" t="s">
         <v>166</v>
       </c>
-      <c r="C9" s="334"/>
-      <c r="D9" s="334"/>
-      <c r="E9" s="334"/>
-      <c r="F9" s="334"/>
-      <c r="G9" s="334"/>
-      <c r="H9" s="334"/>
-      <c r="I9" s="334"/>
-      <c r="J9" s="334"/>
-      <c r="K9" s="334"/>
-      <c r="L9" s="334"/>
+      <c r="C9" s="322"/>
+      <c r="D9" s="322"/>
+      <c r="E9" s="322"/>
+      <c r="F9" s="322"/>
+      <c r="G9" s="322"/>
+      <c r="H9" s="322"/>
+      <c r="I9" s="322"/>
+      <c r="J9" s="322"/>
+      <c r="K9" s="322"/>
+      <c r="L9" s="322"/>
       <c r="M9" s="288" t="s">
         <v>167</v>
       </c>
@@ -6275,11 +6275,11 @@
         <v>303212</v>
       </c>
       <c r="L15" s="299"/>
-      <c r="M15" s="335" t="s">
+      <c r="M15" s="323" t="s">
         <v>180</v>
       </c>
-      <c r="N15" s="336"/>
-      <c r="O15" s="336"/>
+      <c r="N15" s="324"/>
+      <c r="O15" s="324"/>
       <c r="P15" s="300"/>
       <c r="Q15" s="300"/>
       <c r="R15" s="300"/>
@@ -23430,7 +23430,7 @@
         <v>264</v>
       </c>
       <c r="G76" s="148">
-        <f t="shared" ref="G76:G107" si="5">F76-E76</f>
+        <f t="shared" ref="G76:G92" si="5">F76-E76</f>
         <v>155.32037839999998</v>
       </c>
       <c r="H76" s="155">
@@ -30502,7 +30502,7 @@
         <v>20</v>
       </c>
       <c r="J131" s="268">
-        <f t="shared" ref="J131:J162" si="4">IFERROR(I131/(H131+I131),"")</f>
+        <f t="shared" ref="J131:J139" si="4">IFERROR(I131/(H131+I131),"")</f>
         <v>8.0000000000000004E-4</v>
       </c>
       <c r="K131" s="265"/>
@@ -31005,17 +31005,17 @@
       <c r="A1" s="337" t="s">
         <v>266</v>
       </c>
-      <c r="B1" s="334"/>
-      <c r="C1" s="334"/>
-      <c r="D1" s="334"/>
-      <c r="E1" s="334"/>
-      <c r="F1" s="334"/>
-      <c r="G1" s="334"/>
-      <c r="H1" s="334"/>
-      <c r="I1" s="334"/>
-      <c r="J1" s="334"/>
-      <c r="K1" s="334"/>
-      <c r="L1" s="334"/>
+      <c r="B1" s="322"/>
+      <c r="C1" s="322"/>
+      <c r="D1" s="322"/>
+      <c r="E1" s="322"/>
+      <c r="F1" s="322"/>
+      <c r="G1" s="322"/>
+      <c r="H1" s="322"/>
+      <c r="I1" s="322"/>
+      <c r="J1" s="322"/>
+      <c r="K1" s="322"/>
+      <c r="L1" s="322"/>
       <c r="M1" s="338"/>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
@@ -45911,13 +45911,13 @@
       <c r="A1" s="339" t="s">
         <v>314</v>
       </c>
-      <c r="B1" s="334"/>
-      <c r="C1" s="334"/>
-      <c r="D1" s="334"/>
-      <c r="E1" s="334"/>
-      <c r="F1" s="334"/>
-      <c r="G1" s="334"/>
-      <c r="H1" s="334"/>
+      <c r="B1" s="322"/>
+      <c r="C1" s="322"/>
+      <c r="D1" s="322"/>
+      <c r="E1" s="322"/>
+      <c r="F1" s="322"/>
+      <c r="G1" s="322"/>
+      <c r="H1" s="322"/>
       <c r="I1" s="45" t="s">
         <v>1</v>
       </c>
@@ -48707,7 +48707,7 @@
         <v>0</v>
       </c>
       <c r="H79" s="167">
-        <f t="shared" ref="H79:H110" si="3">E79+F79-G79</f>
+        <f t="shared" ref="H79:H94" si="3">E79+F79-G79</f>
         <v>0</v>
       </c>
       <c r="I79" s="166"/>
@@ -56587,15 +56587,15 @@
     </sortState>
   </autoFilter>
   <mergeCells count="9">
+    <mergeCell ref="A92:K92"/>
+    <mergeCell ref="A23:K23"/>
+    <mergeCell ref="A65:K65"/>
+    <mergeCell ref="A81:K81"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A75:K75"/>
     <mergeCell ref="A34:K34"/>
     <mergeCell ref="A12:K12"/>
     <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A92:K92"/>
-    <mergeCell ref="A23:K23"/>
-    <mergeCell ref="A65:K65"/>
-    <mergeCell ref="A81:K81"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
